--- a/artfynd/A 16246-2023 artfynd.xlsx
+++ b/artfynd/A 16246-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16246-2023 artfynd.xlsx
+++ b/artfynd/A 16246-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,7 +1786,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97029252</v>
+        <v>97029335</v>
       </c>
       <c r="B11" t="n">
         <v>96334</v>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513429.7255311666</v>
+        <v>513469.7843899107</v>
       </c>
       <c r="R11" t="n">
-        <v>6699561.135511848</v>
+        <v>6699560.296678495</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1876,11 +1876,6 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1908,7 +1903,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97029335</v>
+        <v>97029403</v>
       </c>
       <c r="B12" t="n">
         <v>96334</v>
@@ -1952,10 +1947,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513469.7843899107</v>
+        <v>513457.2732693055</v>
       </c>
       <c r="R12" t="n">
-        <v>6699560.296678495</v>
+        <v>6699600.240135415</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2025,7 +2020,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97029403</v>
+        <v>97029185</v>
       </c>
       <c r="B13" t="n">
         <v>96334</v>
@@ -2069,10 +2064,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513457.2732693055</v>
+        <v>513373.4462338292</v>
       </c>
       <c r="R13" t="n">
-        <v>6699600.240135415</v>
+        <v>6699535.254766048</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2142,7 +2137,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97029185</v>
+        <v>97029325</v>
       </c>
       <c r="B14" t="n">
         <v>96334</v>
@@ -2186,10 +2181,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513373.4462338292</v>
+        <v>513450.9967232898</v>
       </c>
       <c r="R14" t="n">
-        <v>6699535.254766048</v>
+        <v>6699559.23952985</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2259,10 +2254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97029325</v>
+        <v>97012903</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
+        <v>94121</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2271,25 +2266,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2303,13 +2298,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513450.9967232898</v>
+        <v>513477.6323064802</v>
       </c>
       <c r="R15" t="n">
-        <v>6699559.23952985</v>
+        <v>6699577.605482201</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2338,7 +2333,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2348,7 +2343,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,132 +2359,15 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>97012903</v>
-      </c>
-      <c r="B16" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>53</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Ösjöbäcken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>513477.6323064802</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6699577.605482201</v>
-      </c>
-      <c r="S16" t="n">
-        <v>25</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2021-11-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2021-11-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Lars-Erik Nilsson, Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
